--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-order.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T14:51:40+00:00</t>
+    <t>2025-01-14T21:51:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-order.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T21:51:01+00:00</t>
+    <t>2025-01-15T14:08:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -409,11 +409,9 @@
     <t>Order.id</t>
   </si>
   <si>
-    <t>Identifiant de la prescription :
-Obligatoire pour :
-un CR de biologie pour porter l’Order Placer Number (numéro de la prescription attribué par le prescripteur) / 
-un CR d’imagerie pour porter l'Order Placer Number (numéro de la demande attribué par le demandeur), avec l'attribut @root 
-contenant l'autorité d'affectation et l'attribut @extension contenant l'identifiant géré par cette autorité.</t>
+    <t>Identifiant de la prescription, obligatoire pour :
+- un CR de biologie pour porter l’Order Placer Number (numéro de la prescription attribué par le prescripteur)
+- un CR d’imagerie pour porter l'Order Placer Number (numéro de la demande attribué par le demandeur), avec l'attribut @root contenant l'autorité d'affectation et l'attribut @extension contenant l'identifiant géré par cette autorité.</t>
   </si>
   <si>
     <t>Order.id.nullFlavor</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-order.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-order.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="145">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-15T14:08:36+00:00</t>
+    <t>2025-01-17T15:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -311,6 +311,10 @@
   </si>
   <si>
     <t>InfrastructureRoot.typeId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">II-1:An II instance must have either a root or an nullFlavor. {root.exists() or nullFlavor.exists()}
+</t>
   </si>
   <si>
     <t>Order.typeId.nullFlavor</t>
@@ -1310,7 +1314,7 @@
         <v>74</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>74</v>
@@ -1318,10 +1322,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1419,17 +1423,17 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>80</v>
@@ -1447,11 +1451,11 @@
         <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1502,7 +1506,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -1522,17 +1526,17 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>80</v>
@@ -1550,11 +1554,11 @@
         <v>74</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1605,7 +1609,7 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -1625,17 +1629,17 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>75</v>
@@ -1653,11 +1657,11 @@
         <v>74</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1666,7 +1670,7 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S9" t="s" s="2">
         <v>74</v>
@@ -1708,7 +1712,7 @@
         <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -1728,17 +1732,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>75</v>
@@ -1756,11 +1760,11 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1811,7 +1815,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -1831,10 +1835,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1861,7 +1865,7 @@
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1912,7 +1916,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -1932,10 +1936,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1965,7 +1969,7 @@
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
@@ -1991,7 +1995,7 @@
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>74</v>
@@ -2009,7 +2013,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -2029,10 +2033,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2066,7 +2070,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>74</v>
@@ -2088,7 +2092,7 @@
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>74</v>
@@ -2106,7 +2110,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -2126,10 +2130,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2155,7 +2159,7 @@
         <v>95</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
@@ -2207,7 +2211,7 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>75</v>
@@ -2227,10 +2231,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2328,17 +2332,17 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E16" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F16" t="s" s="2">
         <v>80</v>
@@ -2356,11 +2360,11 @@
         <v>74</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L16" s="2"/>
       <c r="M16" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2411,7 +2415,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -2431,17 +2435,17 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F17" t="s" s="2">
         <v>80</v>
@@ -2459,11 +2463,11 @@
         <v>74</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2514,7 +2518,7 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -2534,17 +2538,17 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E18" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F18" t="s" s="2">
         <v>75</v>
@@ -2562,13 +2566,13 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2619,7 +2623,7 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -2639,17 +2643,17 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F19" t="s" s="2">
         <v>80</v>
@@ -2667,13 +2671,13 @@
         <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2724,7 +2728,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -2744,10 +2748,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2770,7 +2774,7 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
@@ -2799,11 +2803,11 @@
         <v>74</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>74</v>
@@ -2821,7 +2825,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -2841,10 +2845,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2867,7 +2871,7 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
@@ -2896,29 +2900,29 @@
         <v>74</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Y21" s="2"/>
       <c r="Z21" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF21" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="AA21" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB21" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD21" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE21" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-order.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T15:05:21+00:00</t>
+    <t>2025-02-03T10:34:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-order.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T10:34:19+00:00</t>
+    <t>2025-02-05T14:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-order.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T14:18:33+00:00</t>
+    <t>2025-02-05T15:17:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-order.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T15:17:43+00:00</t>
+    <t>2025-02-05T15:35:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-order.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T15:35:39+00:00</t>
+    <t>2025-02-06T13:21:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>order représente la prescription à l’origine de l’acte dont résulte le document.</t>
+    <t>L'élément de l'en-tête du CDA order permet de représenter la prescription à l’origine de l’acte dont résulte le document.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-order.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-06T13:21:10+00:00</t>
+    <t>2025-02-06T13:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
